--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2024_los_lagos.xlsx
@@ -189,7 +189,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:22</t>
+    <t xml:space="preserve">2026-09-09 20:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2024_los_lagos.xlsx
@@ -189,7 +189,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:20</t>
+    <t xml:space="preserve">2026-09-17 03:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2024_los_lagos.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2024_los_lagos.xlsx
@@ -189,7 +189,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 03:27</t>
+    <t xml:space="preserve">2026-10-05 21:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
